--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260917.xlsx
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
